--- a/Employee_Reports_wi52/Bonifacio Arano Bayer Q0557.xlsx
+++ b/Employee_Reports_wi52/Bonifacio Arano Bayer Q0557.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1207,11 +1207,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1256,11 +1256,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1305,11 +1305,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
